--- a/data/trans_orig/IQ27A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, referida por progenitor/a</t>
+          <t>Talla media, en centímetros, declarada por progenitor/a (tasa de respuesta: 90,55%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,69 +716,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>116,53; 130,07</t>
+          <t>116,45; 129,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>115,06; 130,85</t>
+          <t>115,14; 130,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116,48; 131,34</t>
+          <t>117,47; 131,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112,19; 128,54</t>
+          <t>112,86; 128,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>119,37; 135,26</t>
+          <t>118,35; 135,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>113,88; 130,05</t>
+          <t>113,35; 130,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>111,66; 130,24</t>
+          <t>112,25; 130,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121,65; 134,79</t>
+          <t>121,42; 134,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>120,19; 130,77</t>
+          <t>119,95; 130,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116,09; 127,79</t>
+          <t>116,05; 127,82</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116,56; 127,91</t>
+          <t>117,4; 128,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>119,29; 129,54</t>
+          <t>118,76; 129,48</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>117,94; 128,93</t>
+          <t>118,54; 128,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>115,68; 126,74</t>
+          <t>115,86; 126,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119,73; 130,26</t>
+          <t>119,07; 129,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131,84; 150,24</t>
+          <t>131,95; 150,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>125,88; 137,59</t>
+          <t>126,53; 137,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>118,09; 128,58</t>
+          <t>118,77; 128,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>119,94; 129,95</t>
+          <t>119,67; 129,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>130,56; 142,31</t>
+          <t>130,61; 142,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>123,99; 131,67</t>
+          <t>124,32; 131,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118,45; 126,22</t>
+          <t>118,79; 126,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>120,9; 128,22</t>
+          <t>121,03; 128,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>132,86; 144,94</t>
+          <t>132,93; 144,35</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>120,95; 134,07</t>
+          <t>120,5; 133,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>110,78; 123,29</t>
+          <t>110,8; 123,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117,0; 130,04</t>
+          <t>117,43; 130,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124,67; 136,35</t>
+          <t>125,47; 136,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>120,68; 132,85</t>
+          <t>120,95; 132,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>118,18; 131,18</t>
+          <t>117,86; 131,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>118,55; 129,6</t>
+          <t>118,29; 129,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>129,44; 141,7</t>
+          <t>129,24; 142,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122,9; 131,73</t>
+          <t>122,03; 131,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116,63; 125,7</t>
+          <t>116,82; 125,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119,53; 128,68</t>
+          <t>119,87; 128,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>128,96; 137,31</t>
+          <t>129,17; 137,5</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>121,42; 133,02</t>
+          <t>121,41; 133,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>117,5; 130,1</t>
+          <t>117,18; 129,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115,32; 130,55</t>
+          <t>115,02; 130,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128,16; 139,79</t>
+          <t>128,5; 139,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>123,62; 134,82</t>
+          <t>123,9; 135,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>116,99; 129,57</t>
+          <t>116,63; 129,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>120,58; 135,49</t>
+          <t>121,33; 134,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>134,63; 148,41</t>
+          <t>133,84; 147,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>124,05; 132,53</t>
+          <t>124,34; 132,6</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119,27; 128,29</t>
+          <t>119,05; 127,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119,99; 131,16</t>
+          <t>119,99; 130,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>132,91; 143,33</t>
+          <t>133,24; 142,98</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>116,08; 131,29</t>
+          <t>117,54; 131,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>114,63; 134,29</t>
+          <t>114,61; 134,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112,81; 126,15</t>
+          <t>112,53; 126,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123,24; 136,68</t>
+          <t>122,93; 136,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>115,95; 131,39</t>
+          <t>116,29; 132,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>116,15; 136,44</t>
+          <t>115,96; 136,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>119,62; 135,38</t>
+          <t>120,2; 135,17</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>133,23; 145,46</t>
+          <t>133,87; 145,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>118,71; 129,05</t>
+          <t>119,0; 129,32</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118,6; 132,39</t>
+          <t>118,86; 131,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118,7; 129,36</t>
+          <t>118,27; 128,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>130,37; 140,06</t>
+          <t>130,6; 140,17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1416,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121,47; 134,89</t>
+          <t>121,56; 134,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115,43; 129,93</t>
+          <t>115,8; 129,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>120,58; 134,45</t>
+          <t>121,16; 134,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121,36; 134,75</t>
+          <t>121,99; 135,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>125,33; 138,97</t>
+          <t>125,2; 138,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>116,66; 133,21</t>
+          <t>115,99; 132,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119,71; 133,6</t>
+          <t>119,85; 135,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>117,15; 130,96</t>
+          <t>117,38; 131,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124,76; 134,54</t>
+          <t>125,27; 134,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>118,33; 129,77</t>
+          <t>118,42; 129,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122,07; 132,64</t>
+          <t>122,28; 132,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>121,75; 131,29</t>
+          <t>121,31; 130,93</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>121,67; 130,2</t>
+          <t>121,59; 130,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>115,4; 125,77</t>
+          <t>115,8; 125,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118,84; 127,26</t>
+          <t>118,55; 126,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128,78; 139,24</t>
+          <t>129,22; 139,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>119,48; 129,46</t>
+          <t>119,42; 129,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>115,68; 125,47</t>
+          <t>115,78; 125,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>119,47; 128,77</t>
+          <t>119,64; 128,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>140,32; 151,41</t>
+          <t>140,25; 150,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>121,65; 128,14</t>
+          <t>121,81; 128,44</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117,05; 124,06</t>
+          <t>117,32; 123,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120,58; 126,64</t>
+          <t>120,54; 126,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>137,06; 144,79</t>
+          <t>136,95; 144,6</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>122,69; 130,77</t>
+          <t>123,0; 131,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>117,18; 125,26</t>
+          <t>117,12; 125,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116,96; 124,58</t>
+          <t>116,86; 124,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131,47; 138,21</t>
+          <t>131,62; 138,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>122,45; 131,42</t>
+          <t>122,12; 130,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>117,72; 125,92</t>
+          <t>118,03; 126,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>118,25; 125,92</t>
+          <t>117,91; 125,78</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>132,58; 140,58</t>
+          <t>132,24; 140,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>123,82; 129,67</t>
+          <t>123,61; 129,77</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>118,69; 124,54</t>
+          <t>119,03; 124,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118,36; 123,86</t>
+          <t>118,46; 123,89</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>133,38; 138,64</t>
+          <t>133,23; 138,47</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>124,21; 128,03</t>
+          <t>124,21; 128,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119,23; 123,39</t>
+          <t>119,47; 123,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>121,04; 125,13</t>
+          <t>121,09; 125,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>131,21; 137,15</t>
+          <t>131,05; 137,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>125,69; 129,42</t>
+          <t>125,39; 129,53</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>120,6; 124,97</t>
+          <t>120,89; 125,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>122,47; 126,53</t>
+          <t>122,44; 126,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>134,73; 139,46</t>
+          <t>134,57; 139,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>125,5; 128,29</t>
+          <t>125,42; 128,28</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>120,65; 123,68</t>
+          <t>120,6; 123,63</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122,35; 125,16</t>
+          <t>122,48; 125,23</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>133,61; 137,29</t>
+          <t>133,66; 137,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>116,45; 129,87</t>
+          <t>115,72; 130,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>115,14; 130,25</t>
+          <t>114,59; 129,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117,47; 131,73</t>
+          <t>116,8; 131,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112,86; 128,92</t>
+          <t>112,27; 128,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>118,35; 135,35</t>
+          <t>119,04; 135,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>113,35; 130,68</t>
+          <t>112,57; 129,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>112,25; 130,01</t>
+          <t>112,46; 129,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121,42; 134,01</t>
+          <t>121,58; 134,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119,95; 130,38</t>
+          <t>119,67; 130,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116,05; 127,82</t>
+          <t>115,96; 127,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117,4; 128,57</t>
+          <t>116,47; 128,24</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>118,76; 129,48</t>
+          <t>119,07; 129,58</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>118,54; 128,72</t>
+          <t>117,9; 129,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>115,86; 126,83</t>
+          <t>115,44; 126,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119,07; 129,73</t>
+          <t>118,93; 129,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131,95; 150,8</t>
+          <t>131,74; 148,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,53; 137,78</t>
+          <t>126,05; 136,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>118,77; 128,72</t>
+          <t>118,5; 129,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>119,67; 129,69</t>
+          <t>119,51; 130,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>130,61; 142,52</t>
+          <t>130,69; 142,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124,32; 131,78</t>
+          <t>124,05; 131,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118,79; 126,25</t>
+          <t>118,5; 126,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121,03; 128,31</t>
+          <t>121,02; 128,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>132,93; 144,35</t>
+          <t>132,95; 144,54</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>120,5; 133,71</t>
+          <t>119,98; 133,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>110,8; 123,33</t>
+          <t>110,91; 123,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117,43; 130,23</t>
+          <t>117,21; 130,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125,47; 136,35</t>
+          <t>124,89; 136,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>120,95; 132,89</t>
+          <t>121,3; 132,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>117,86; 131,3</t>
+          <t>118,24; 131,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>118,29; 129,68</t>
+          <t>118,31; 130,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>129,24; 142,22</t>
+          <t>128,27; 141,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122,03; 131,51</t>
+          <t>122,85; 131,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116,82; 125,39</t>
+          <t>116,53; 125,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119,87; 128,64</t>
+          <t>120,09; 128,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>129,17; 137,5</t>
+          <t>129,14; 137,64</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>121,41; 133,87</t>
+          <t>121,52; 133,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>117,18; 129,78</t>
+          <t>117,72; 130,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115,02; 130,81</t>
+          <t>115,04; 131,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128,5; 139,88</t>
+          <t>127,92; 140,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>123,9; 135,25</t>
+          <t>123,9; 134,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>116,63; 129,45</t>
+          <t>116,66; 129,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>121,33; 134,85</t>
+          <t>120,0; 134,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>133,84; 147,98</t>
+          <t>133,86; 147,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>124,34; 132,6</t>
+          <t>124,44; 132,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119,05; 127,74</t>
+          <t>119,34; 128,4</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119,99; 130,8</t>
+          <t>120,35; 130,97</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>133,24; 142,98</t>
+          <t>133,48; 143,37</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>117,54; 131,57</t>
+          <t>117,09; 130,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>114,61; 134,54</t>
+          <t>114,46; 132,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112,53; 126,08</t>
+          <t>112,78; 126,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122,93; 136,6</t>
+          <t>123,47; 136,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>116,29; 132,66</t>
+          <t>115,75; 131,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>115,96; 136,69</t>
+          <t>116,28; 136,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>120,2; 135,17</t>
+          <t>119,96; 135,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>133,87; 145,62</t>
+          <t>133,96; 146,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>119,0; 129,32</t>
+          <t>118,18; 129,19</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118,86; 131,99</t>
+          <t>118,43; 132,65</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118,27; 128,39</t>
+          <t>118,67; 129,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>130,6; 140,17</t>
+          <t>130,46; 139,67</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121,56; 134,36</t>
+          <t>121,47; 134,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115,8; 129,9</t>
+          <t>115,61; 129,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121,16; 134,5</t>
+          <t>121,04; 134,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121,99; 135,44</t>
+          <t>121,96; 135,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>125,2; 138,18</t>
+          <t>125,03; 139,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115,99; 132,91</t>
+          <t>115,9; 133,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119,85; 135,03</t>
+          <t>119,69; 134,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>117,38; 131,43</t>
+          <t>117,9; 132,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125,27; 134,73</t>
+          <t>125,0; 134,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>118,42; 129,67</t>
+          <t>117,52; 129,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122,28; 132,11</t>
+          <t>122,6; 132,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>121,31; 130,93</t>
+          <t>121,13; 130,93</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>121,59; 130,42</t>
+          <t>121,75; 130,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>115,8; 125,54</t>
+          <t>115,81; 126,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118,55; 126,86</t>
+          <t>118,24; 127,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129,22; 139,46</t>
+          <t>129,38; 139,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>119,42; 129,02</t>
+          <t>119,3; 129,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>115,78; 125,1</t>
+          <t>116,07; 125,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>119,64; 128,58</t>
+          <t>119,83; 128,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>140,25; 150,97</t>
+          <t>140,04; 151,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>121,81; 128,44</t>
+          <t>121,84; 128,3</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117,32; 123,95</t>
+          <t>117,27; 123,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120,54; 126,88</t>
+          <t>120,66; 126,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>136,95; 144,6</t>
+          <t>136,74; 144,71</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>123,0; 131,1</t>
+          <t>123,23; 130,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>117,12; 125,33</t>
+          <t>117,19; 125,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116,86; 124,67</t>
+          <t>116,63; 124,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131,62; 138,4</t>
+          <t>131,49; 138,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>122,12; 130,87</t>
+          <t>122,4; 130,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>118,03; 126,08</t>
+          <t>118,15; 126,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>117,91; 125,78</t>
+          <t>117,93; 125,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>132,24; 140,33</t>
+          <t>132,5; 140,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>123,61; 129,77</t>
+          <t>123,88; 129,88</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119,03; 124,9</t>
+          <t>118,96; 124,53</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118,46; 123,89</t>
+          <t>118,32; 123,66</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>133,23; 138,47</t>
+          <t>133,41; 138,6</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>124,21; 128,07</t>
+          <t>124,07; 128,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119,47; 123,72</t>
+          <t>119,31; 123,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>121,09; 125,16</t>
+          <t>121,11; 124,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>131,05; 137,31</t>
+          <t>131,1; 137,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>125,39; 129,53</t>
+          <t>125,48; 129,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>120,89; 125,19</t>
+          <t>120,66; 124,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>122,44; 126,57</t>
+          <t>122,5; 126,43</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>134,57; 139,15</t>
+          <t>134,74; 139,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>125,42; 128,28</t>
+          <t>125,32; 128,2</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>120,6; 123,63</t>
+          <t>120,75; 123,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122,48; 125,23</t>
+          <t>122,25; 125,1</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>133,66; 137,31</t>
+          <t>133,62; 137,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ27A-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>127,14</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>121,99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>120,93</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>128,83</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>123,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>122,83</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>124,35</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>121,9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>127,14</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>121,99</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>120,93</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>127,81</t>
+          <t>125,27</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>124,93</t>
+          <t>127,12</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>115,72; 130,71</t>
+          <t>119,37; 135,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114,59; 129,92</t>
+          <t>113,88; 130,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>116,8; 131,71</t>
+          <t>111,66; 130,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112,27; 128,31</t>
+          <t>122,58; 136,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>119,04; 135,24</t>
+          <t>116,53; 130,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>112,57; 129,75</t>
+          <t>115,06; 130,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>112,46; 129,52</t>
+          <t>116,48; 131,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>121,58; 134,8</t>
+          <t>119,44; 131,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119,67; 130,56</t>
+          <t>120,19; 130,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115,96; 127,91</t>
+          <t>116,09; 127,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116,47; 128,24</t>
+          <t>116,56; 127,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>119,07; 129,58</t>
+          <t>122,56; 131,42</t>
         </is>
       </c>
     </row>
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>131,81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>123,48</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125,12</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>136,94</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>123,73</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>121,38</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>124,55</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>139,62</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>131,81</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>123,48</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>125,12</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>134,52</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>127,96</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>122,45</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>124,83</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>135,81</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>127,96</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>122,45</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124,83</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>137,73</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>117,9; 129,21</t>
+          <t>125,88; 137,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>115,44; 126,87</t>
+          <t>118,09; 128,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>118,93; 129,78</t>
+          <t>119,94; 129,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131,74; 148,94</t>
+          <t>131,63; 143,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,05; 136,46</t>
+          <t>117,94; 128,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>118,5; 129,03</t>
+          <t>115,68; 126,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>119,51; 130,1</t>
+          <t>119,73; 130,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>130,69; 142,62</t>
+          <t>128,52; 139,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>124,05; 131,79</t>
+          <t>123,99; 131,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118,5; 126,12</t>
+          <t>118,45; 126,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121,02; 128,43</t>
+          <t>120,9; 128,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>132,95; 144,54</t>
+          <t>132,02; 139,68</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126,98</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>124,71</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>124,38</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>136,1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>127,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>117,37</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>124,13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>130,82</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>126,98</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>124,71</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>124,38</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>135,52</t>
+          <t>131,52</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>133,32</t>
+          <t>133,85</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>119,98; 133,71</t>
+          <t>120,68; 132,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>110,91; 123,15</t>
+          <t>118,18; 131,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>117,21; 130,12</t>
+          <t>118,55; 129,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124,89; 136,29</t>
+          <t>130,15; 142,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>121,3; 132,72</t>
+          <t>120,95; 134,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>118,24; 131,07</t>
+          <t>110,78; 123,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>118,31; 130,62</t>
+          <t>117,0; 130,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,27; 141,28</t>
+          <t>125,7; 137,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>122,85; 131,44</t>
+          <t>122,9; 131,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116,53; 125,68</t>
+          <t>116,63; 125,7</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120,09; 128,76</t>
+          <t>119,53; 128,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>129,14; 137,64</t>
+          <t>129,66; 137,72</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>129,43</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>123,22</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>128,22</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>141,39</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>127,4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>123,82</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>123,13</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>134,49</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>129,43</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>123,22</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>128,22</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>140,83</t>
+          <t>136,15</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>138,01</t>
+          <t>138,95</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>121,52; 133,12</t>
+          <t>123,62; 134,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>117,72; 130,11</t>
+          <t>116,99; 129,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115,04; 131,08</t>
+          <t>120,58; 135,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127,92; 140,18</t>
+          <t>135,49; 148,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>123,9; 134,71</t>
+          <t>121,42; 133,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>116,66; 129,28</t>
+          <t>117,5; 130,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>120,0; 134,5</t>
+          <t>115,32; 130,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>133,86; 147,27</t>
+          <t>129,91; 141,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>124,44; 132,61</t>
+          <t>124,05; 132,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119,34; 128,4</t>
+          <t>119,27; 128,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120,35; 130,97</t>
+          <t>119,99; 131,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>133,48; 143,37</t>
+          <t>133,89; 143,49</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>124,08</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>126,24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>127,86</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141,17</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>124,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>124,66</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>119,85</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>129,94</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>124,08</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>126,24</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>127,86</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>139,82</t>
+          <t>130,66</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>135,27</t>
+          <t>136,17</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>117,09; 130,75</t>
+          <t>115,95; 131,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>114,46; 132,85</t>
+          <t>116,15; 136,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112,78; 126,08</t>
+          <t>119,62; 135,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>123,47; 136,39</t>
+          <t>134,94; 146,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>115,75; 131,9</t>
+          <t>116,08; 131,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>116,28; 136,1</t>
+          <t>114,63; 134,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>119,96; 135,65</t>
+          <t>112,81; 126,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>133,96; 146,21</t>
+          <t>124,46; 137,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>118,18; 129,19</t>
+          <t>118,71; 129,05</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118,43; 132,65</t>
+          <t>118,6; 132,39</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118,67; 129,04</t>
+          <t>118,7; 129,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>130,46; 139,67</t>
+          <t>131,3; 141,0</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>132,1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>125,31</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>127,16</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>126,53</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>127,98</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>123,01</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>127,82</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128,71</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>132,1</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>125,31</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>127,16</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>124,48</t>
+          <t>130,71</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>126,37</t>
+          <t>128,53</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121,47; 134,79</t>
+          <t>125,33; 138,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>115,61; 129,6</t>
+          <t>116,66; 133,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121,04; 134,69</t>
+          <t>119,71; 133,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121,96; 135,36</t>
+          <t>119,25; 132,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>125,03; 139,16</t>
+          <t>121,47; 134,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115,9; 133,1</t>
+          <t>115,43; 129,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119,69; 134,25</t>
+          <t>120,58; 134,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>117,9; 132,02</t>
+          <t>123,3; 136,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>125,0; 134,28</t>
+          <t>124,76; 134,54</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>117,52; 129,55</t>
+          <t>118,33; 129,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122,6; 132,62</t>
+          <t>122,07; 132,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>121,13; 130,93</t>
+          <t>123,9; 133,33</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124,22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>120,27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>124,08</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144,22</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>125,94</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>120,76</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>123,1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>135,1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>124,22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>120,27</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>124,08</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>144,59</t>
+          <t>136,91</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>140,44</t>
+          <t>140,87</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>121,75; 130,27</t>
+          <t>119,48; 129,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>115,81; 126,35</t>
+          <t>115,68; 125,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>118,24; 127,46</t>
+          <t>119,47; 128,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>129,38; 139,13</t>
+          <t>140,3; 148,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>119,3; 129,15</t>
+          <t>121,67; 130,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>116,07; 125,26</t>
+          <t>115,4; 125,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>119,83; 128,44</t>
+          <t>118,84; 127,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>140,04; 151,03</t>
+          <t>132,46; 140,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>121,84; 128,3</t>
+          <t>121,65; 128,14</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117,27; 123,85</t>
+          <t>117,05; 124,06</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120,66; 126,79</t>
+          <t>120,58; 126,64</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>136,74; 144,71</t>
+          <t>137,9; 144,03</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>126,58</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>122,17</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>121,82</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>138,17</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>127,07</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>121,28</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>120,55</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>135,12</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>126,58</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>122,17</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>121,82</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136,69</t>
+          <t>136,72</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>135,97</t>
+          <t>137,49</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>123,23; 130,9</t>
+          <t>122,45; 131,42</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>117,19; 125,58</t>
+          <t>117,72; 125,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>116,63; 124,11</t>
+          <t>118,25; 125,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131,49; 138,39</t>
+          <t>134,16; 141,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>122,4; 130,59</t>
+          <t>122,69; 130,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>118,15; 126,68</t>
+          <t>117,18; 125,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>117,93; 125,63</t>
+          <t>116,96; 124,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>132,5; 140,1</t>
+          <t>133,17; 139,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>123,88; 129,88</t>
+          <t>123,82; 129,67</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>118,96; 124,53</t>
+          <t>118,69; 124,54</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>118,32; 123,66</t>
+          <t>118,36; 123,86</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>133,41; 138,6</t>
+          <t>135,02; 140,07</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>127,6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>122,81</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>124,47</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>137,89</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>126,08</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>121,45</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>123,11</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>133,48</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>127,6</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>122,81</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>124,47</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>136,87</t>
+          <t>134,06</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>135,29</t>
+          <t>136,09</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>124,07; 128,06</t>
+          <t>125,69; 129,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>119,31; 123,53</t>
+          <t>120,6; 124,97</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>121,11; 124,97</t>
+          <t>122,47; 126,53</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>131,1; 137,36</t>
+          <t>135,81; 140,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>125,48; 129,75</t>
+          <t>124,21; 128,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>120,66; 124,97</t>
+          <t>119,23; 123,39</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>122,5; 126,43</t>
+          <t>121,04; 125,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>134,74; 139,18</t>
+          <t>132,4; 135,87</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>125,32; 128,2</t>
+          <t>125,5; 128,29</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>120,75; 123,51</t>
+          <t>120,65; 123,68</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122,25; 125,1</t>
+          <t>122,35; 125,16</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>133,62; 137,31</t>
+          <t>134,74; 137,44</t>
         </is>
       </c>
     </row>
